--- a/daily_matches/job_matches_2026-05-06.xlsx
+++ b/daily_matches/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,157 +468,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kinesis, CI/CD, Redshift, Kafka, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, RAG, Copilot, BigQuery, Dataflow, Docker, Kubernetes, AKS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kinesis, CI/CD, Redshift, Kafka, PostgreSQL, MongoDB</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, MLflow, CI/CD, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kinesis, CI/CD, Redshift, Kafka, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Azure ML, Synapse, CI/CD, Git, Databricks, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c0e5823a5a0a57</t>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Gen AI Engineer + Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zenith Algorithms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kinesis, CI/CD, Redshift, Kafka, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=846e759a29fb1c3c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,104 +626,104 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kinesis, CI/CD, Redshift, Kafka, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, TensorFlow, PyTorch, XGBoost</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
+          <t>https://www.indeed.com/viewjob?jk=034c064cc8e4b3b6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kinesis, CI/CD, Redshift, Kafka, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c63fb90b07eaf3</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Kinesis, CI/CD, Redshift, Kafka, PostgreSQL, MongoDB</t>
+          <t>Data Scientist, RAG, Copilot, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67c28cbc09b5ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer – Data Pipelines / ETL / MLOps</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALTEN</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, MLflow, Snowflake, BigQuery, Redshift, Kafka, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e340b6546ba7391</t>
+          <t>https://www.indeed.com/viewjob?jk=4c086ab6d03a3397</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GoEngineer</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Redshift, BigQuery, Synapse, Snowflake, BigQuery, Redshift, Power BI</t>
+          <t>RAG, S3, CI/CD, Terraform, Git, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4746d2b33fc6fce</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AdvanSix</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chester, VA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Hugging Face, Prompt Engineering, Docker, Kubernetes, CI/CD, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd59facc6c2f2d30</t>
+          <t>https://www.indeed.com/viewjob?jk=e23c392ebea778eb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Site Reliability Engineer III- Kafka Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AdvanSix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hopewell, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa359cda3738a834</t>
+          <t>https://www.indeed.com/viewjob?jk=76cd5a335799b66c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Enterprise AI Insights Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AdvanSix</t>
+          <t>Highgate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a7e15ca3527122</t>
+          <t>https://www.indeed.com/viewjob?jk=d68a39f362643ddb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Systems Administrator, Enterprise AI Platforms</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Git, Snowflake, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418fbee27cfc74c5</t>
+          <t>https://www.indeed.com/viewjob?jk=83a6336bdb971ca1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist II-Data Driven Discovery in Biomedicine (D3b)</t>
+          <t>Perception Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,87 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Hadoop, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, YOLO, Docker, CI/CD, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2347b7e19f480a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr Security Engineer (SOAR/Automation) Austin &amp; San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HEB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54041e43238ecd48</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HERE Technologies</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f588035522970b0</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=211d586444e1ab97</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-06.xlsx
+++ b/daily_matches/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, BigQuery, Dataflow, Docker, Kubernetes, AKS, CI/CD, Jenkins</t>
+          <t>Copilot, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=550e29553f2a099b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>AI Fullstack Software Engineer-Intern</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, MLflow, CI/CD, Databricks, Redshift</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
+          <t>https://www.indeed.com/viewjob?jk=5feabecfb6ffbba9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Azure ML, Synapse, CI/CD, Git, Databricks, PostgreSQL</t>
+          <t>RAG, Copilot, S3, Athena, CI/CD, Jenkins, Git, Kafka, Polars, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
+          <t>https://www.indeed.com/viewjob?jk=0e88c480437dd451</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gen AI Engineer + Data Scientist</t>
+          <t>Data Platforms Analyst (National Geographic)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zenith Algorithms</t>
+          <t>National Geographic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Databricks</t>
+          <t>Data Scientist, RAG, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Tableau, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=846e759a29fb1c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=87b0984f17543bf4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, TensorFlow, PyTorch, XGBoost</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c064cc8e4b3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=70c76699683bf4a2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Tableau, MicroStrategy, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Tableau</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Tableau, MicroStrategy, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, Python</t>
+          <t>Redshift, Data Lake, Kinesis, Git, Snowflake, Databricks, Redshift, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c086ab6d03a3397</t>
+          <t>https://www.indeed.com/viewjob?jk=f544b0c492f55ad5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Software Engineer - Cloud Fullstack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, MongoDB, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
+          <t>https://www.indeed.com/viewjob?jk=059fe198bd3f948a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ochsner Health</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Hugging Face, Prompt Engineering, Docker, Kubernetes, CI/CD, R</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e23c392ebea778eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III- Kafka Platform</t>
+          <t>Senior Software Engineer - Cloud Gateway</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, MongoDB, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76cd5a335799b66c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Enterprise AI Insights Associate</t>
+          <t>Software Engineer - DevOps Mobile</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Highgate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68a39f362643ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a6336bdb971ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=92d99019298208f9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Perception Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, YOLO, Docker, CI/CD, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,77 +951,847 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2347b7e19f480a7</t>
+          <t>https://www.indeed.com/viewjob?jk=14f696297699c45d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Security Engineer (SOAR/Automation) Austin &amp; San Antonio, TX</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Glue, FastAPI, Docker, CI/CD, Terraform, Git, PySpark, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54041e43238ecd48</t>
+          <t>https://www.indeed.com/viewjob?jk=36490e4938cafc8b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HERE Technologies</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b224fb124b25e580</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - Ruby on Rails &amp; ReactJS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Checkmate</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6f9b75b3b6b975a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Release Engineer, OTA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, CI/CD, Snowflake, Databricks, Redshift, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fba36cb0f3b563d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr. AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5adff7ab8988c6c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FastAPI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BigQuery, FastAPI, CI/CD, Git, BigQuery, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, Kubernetes, CI/CD, Git, PySpark, Hadoop, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45974a79c5dfc2f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae79bd99177c5d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, LLaMA, Mistral, TensorFlow, PyTorch, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=456433b3574591da</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior DevOps Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6f51dfeaed49375</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer, Fullstack (Developer Productivity)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d1ee3050397b940</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI/ML Research Scientist/Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aspire Tech IT Solution</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2feb75e3ea35414</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Factory HIL Automation and Test Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Normal, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ee4d5b259ce65ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=254187a4c7d9fffa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Fullstack</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1add3cd08fe762d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Release Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a7bfbf94befa2f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Full-Stack (Developer Productivity)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f01703bf2baa5597</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Product Engineer Sr. Java Springboot -</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Allstate Insurance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Jenkins, Git, Kafka, MongoDB, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc00baff49708415</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Digital Collaboration Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Central Ohio Transit Authority</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Power BI, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c1df25ffb734f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI-Driven Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaf2a12ac6b4c67c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>API Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=909abe2b71c9a0a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI &amp; Agentic Engineer – Healthcare Payment Integrity</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Codoxo</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, FAISS, S3, Glue, Athena, Kubernetes, Python, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=211d586444e1ab97</t>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c2a45f9ed1a2d44</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-06.xlsx
+++ b/daily_matches/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Azure ML</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=550e29553f2a099b</t>
+          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Fullstack Software Engineer-Intern</t>
+          <t>AI Engineer Clinical Data Science</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>25.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Snowflake</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5feabecfb6ffbba9</t>
+          <t>https://www.indeed.com/viewjob?jk=47a06a95eff2f8b1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer, AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Athena, CI/CD, Jenkins, Git, Kafka, Polars, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Mistral, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e88c480437dd451</t>
+          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Platforms Analyst (National Geographic)</t>
+          <t>Software Engineer (Agentic AI/Data Engineering)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Geographic</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Tableau, Python</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b0984f17543bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7b48ca42d0998a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, NoSQL</t>
+          <t>S3, Glue, Redshift, Data Lake, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,49 +636,49 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c76699683bf4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Data Science AI Engineer, Advisor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Tableau, MicroStrategy, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Hadoop, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5933d9753dfeaf6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Tableau, MicroStrategy, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
+          <t>https://www.indeed.com/viewjob?jk=58e6cb2fe1ba2899</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, Data Lake, Kinesis, Git, Snowflake, Databricks, Redshift, Kafka, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f544b0c492f55ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Fullstack</t>
+          <t>Senior Data analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, MongoDB, Python</t>
+          <t>Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059fe198bd3f948a</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>SIXT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Quicksight</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=ac34670bb41fef77</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Gateway</t>
+          <t>Enterprise Systems Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Schellman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, MongoDB, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
+          <t>https://www.indeed.com/viewjob?jk=c144b4fb24d4be6a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps Mobile</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, BigQuery, Git, BigQuery, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=41d8c000100c2e3a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Onspring Technologies, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92d99019298208f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4dc9b5039e443a4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Onspring Technologies, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f696297699c45d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>AI and Data Governance Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, FastAPI, Docker, CI/CD, Terraform, Git, PySpark, Python</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36490e4938cafc8b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c402ee4c033c60a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Cloud Networking Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, NoSQL, Python, SQL</t>
+          <t>Docker, CI/CD, Jenkins, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b224fb124b25e580</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Ruby on Rails &amp; ReactJS</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f9b75b3b6b975a</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Release Engineer, OTA</t>
+          <t>Senior Associate Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Redshift, CI/CD, Snowflake, Databricks, Redshift, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Hadoop, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fba36cb0f3b563d9</t>
+          <t>https://www.indeed.com/viewjob?jk=60d5d508ce574d46</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Decision Engine AI Ops Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=73dbdeb85ef41bd2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
+          <t>Sr Software Engineer - Facets application; .Net; C# - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8e8e368729e98f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5adff7ab8988c6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdd586330b5eb21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BigQuery, FastAPI, CI/CD, Git, BigQuery, Kafka, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+          <t>https://www.indeed.com/viewjob?jk=b2952cc86b260a2f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Teambuilderz</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Kubernetes, CI/CD, Git, PySpark, Hadoop, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45974a79c5dfc2f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6a46e10f5f53e217</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Samaritan's Purse</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae79bd99177c5d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c745bbd9873b03e6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Sr. Manufacturing Applications Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Align Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, LLaMA, Mistral, TensorFlow, PyTorch, Python, R, Scala</t>
+          <t>RAG, Copilot, Git, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456433b3574591da</t>
+          <t>https://www.indeed.com/viewjob?jk=19a642fa61f9f727</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Data Scientist - Sr. Consultant Level</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f51dfeaed49375</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc60a31675249d7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack (Developer Productivity)</t>
+          <t>Data Scientist - Sr. Consultant Level</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1ee3050397b940</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4ab1ec97532501</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI/ML Research Scientist/Engineer</t>
+          <t>Data Scientist - Sr. Consultant Level</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aspire Tech IT Solution</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2feb75e3ea35414</t>
+          <t>https://www.indeed.com/viewjob?jk=d792d982edefbc44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Factory HIL Automation and Test Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>NCD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Normal, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, BigQuery, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee4d5b259ce65ea</t>
+          <t>https://www.indeed.com/viewjob?jk=044e7c542b65b781</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, Data Lake, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,287 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254187a4c7d9fffa</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Fullstack</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1add3cd08fe762d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Software Release Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Jenkins, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7bfbf94befa2f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Full-Stack (Developer Productivity)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f01703bf2baa5597</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Product Engineer Sr. Java Springboot -</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Allstate Insurance</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Jenkins, Git, Kafka, MongoDB, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc00baff49708415</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Digital Collaboration Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Central Ohio Transit Authority</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Power BI, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c1df25ffb734f9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf2a12ac6b4c67c</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>API Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, Jenkins, Git, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=909abe2b71c9a0a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>AI &amp; Agentic Engineer – Healthcare Payment Integrity</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Codoxo</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, FAISS, S3, Glue, Athena, Kubernetes, Python, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2a45f9ed1a2d44</t>
+          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-06.xlsx
+++ b/daily_matches/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Better Direct</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Azure ML</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc4f5a1a8294505</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer Clinical Data Science</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, ChromaDB</t>
+          <t>RAG, Redshift, Synapse, Git, Snowflake, Databricks, Redshift, PySpark, Hadoop, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a06a95eff2f8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>AMB Sports + Entertainment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Mistral, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=0fac751a341ffed9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer (Agentic AI/Data Engineering)</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gartner</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Kafka, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7b48ca42d0998a</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Data Lake, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Redshift</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, BigQuery, Git, BigQuery, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
+          <t>https://www.indeed.com/viewjob?jk=991ed2128f9f4a5d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Science AI Engineer, Advisor</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Hadoop, NoSQL</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5933d9753dfeaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=09cec63cf2ebcb0b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Applied Mathematics  Physics Intern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visto360 AI Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, NoSQL</t>
+          <t>AI Engineer, TensorFlow, PyTorch, OpenCV, Docker, Git, Matplotlib, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e6cb2fe1ba2899</t>
+          <t>https://www.indeed.com/viewjob?jk=565e7e6c7d65c54f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>RH Aero Systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Synapse, Data Lake, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c93d027116f419</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data analyst</t>
+          <t>Senior Data Engineer Biloxi 5139</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Keesler Federal Credit Union</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Biloxi, MS, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, Python, SQL</t>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Databricks, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SIXT</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Quicksight</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac34670bb41fef77</t>
+          <t>https://www.indeed.com/viewjob?jk=2f732c876ee23fd3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise Systems Architect</t>
+          <t>Sr. Software Engineer: Frontend</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Schellman</t>
+          <t>LogicGate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, R</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c144b4fb24d4be6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f04003c2d987b1a8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Sr. Software Engineer: Frontend</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>LogicGate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, BigQuery, Git, BigQuery, PySpark, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d8c000100c2e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e73a3c785ad1e1e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer: Frontend</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Onspring Technologies, LLC</t>
+          <t>LogicGate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4dc9b5039e443a4</t>
+          <t>https://www.indeed.com/viewjob?jk=13e08efe5897e8e9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer: Frontend</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Onspring Technologies, LLC</t>
+          <t>LogicGate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
+          <t>https://www.indeed.com/viewjob?jk=de8a47ad97c2d7cf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI and Data Governance Engineer</t>
+          <t>Sr. Software Engineer: Frontend</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>LogicGate</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c402ee4c033c60a</t>
+          <t>https://www.indeed.com/viewjob?jk=fdffc06c5ccc1b8e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Networking Consultant</t>
+          <t>Sr. Software Engineer: Frontend</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LogicGate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Jenkins, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=64d194fe052b34b6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Sr. Software Engineer: Frontend</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>LogicGate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=fed11f229285ca52</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Associate Data Scientist</t>
+          <t>Senior Software Engineer, Security Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Hadoop, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, Snowflake, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60d5d508ce574d46</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7a17ecc5d35899</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Decision Engine AI Ops Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
+          <t>RAG, Synapse, Data Lake, Snowflake, Databricks, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dbdeb85ef41bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Facets application; .Net; C# - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Whitehall, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8e8e368729e98f</t>
+          <t>https://www.indeed.com/viewjob?jk=476365429fdab851</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Machine Learning Engineer II, Burger King, US&amp;C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, Snowflake, Python, SQL, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdd586330b5eb21</t>
+          <t>https://www.indeed.com/viewjob?jk=f87bae5a9ff1cc5b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>RTOS Developer for Medical Devices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Unetixs Vascular, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warwick, RI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Jenkins, Git, MySQL, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,287 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2952cc86b260a2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Teambuilderz</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Dover, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Tableau, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a46e10f5f53e217</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Samaritan's Purse</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Coppell, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c745bbd9873b03e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Sr. Manufacturing Applications Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Align Technology</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19a642fa61f9f727</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Scientist - Sr. Consultant Level</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc60a31675249d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Data Scientist - Sr. Consultant Level</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4ab1ec97532501</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Scientist - Sr. Consultant Level</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Foster City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d792d982edefbc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NCD</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=044e7c542b65b781</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Montefiore Einstein</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Yonkers, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Data Lake, Git, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+          <t>https://www.indeed.com/viewjob?jk=4d757f556f0fd1a1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-06.xlsx
+++ b/daily_matches/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Better Direct</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering</t>
+          <t>RAG, Copilot, Cortex, Redshift, BigQuery, Data Lake, Snowflake, BigQuery, Redshift, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc4f5a1a8294505</t>
+          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Graybar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Clayton, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Synapse, Git, Snowflake, Databricks, Redshift, PySpark, Hadoop, Cassandra</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=82b455422eee9334</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMB Sports + Entertainment</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ontario, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fac751a341ffed9</t>
+          <t>https://www.indeed.com/viewjob?jk=52a8022f39595ebf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Kafka, Hadoop, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Azure ML, MLflow, Docker, CI/CD, GitHub Actions, Git, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6ee13b18ffe86d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>AI Engineer- Senior Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, BigQuery, Git, BigQuery, PySpark, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Docker, Kubernetes, AKS, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ed2128f9f4a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=7921646131415cec</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>AI Engineer- Senior Associate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Docker, Kubernetes, AKS, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cec63cf2ebcb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=86909537359158b4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applied Mathematics  Physics Intern</t>
+          <t>AI Engineer- Senior Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Visto360 AI Inc.</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, TensorFlow, PyTorch, OpenCV, Docker, Git, Matplotlib, Python, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Docker, Kubernetes, AKS, CI/CD, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e7e6c7d65c54f</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc876921c22ef16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RH Aero Systems</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>S3, Glue, Redshift, Kinesis, Docker, CI/CD, Jenkins, Terraform, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c93d027116f419</t>
+          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Biloxi 5139</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Keesler Federal Credit Union</t>
+          <t>SEEQ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Biloxi, MS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Databricks, Power BI, SQL, R, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, Azure ML, Data Lake, CI/CD, Snowflake, Databricks, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
+          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>RNGD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f732c876ee23fd3</t>
+          <t>https://www.indeed.com/viewjob?jk=f8999ba90c762227</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer: Frontend</t>
+          <t>Data Scientist- Senior Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LogicGate</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04003c2d987b1a8</t>
+          <t>https://www.indeed.com/viewjob?jk=16f33a2b9912522b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer: Frontend</t>
+          <t>Data Scientist- Senior Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LogicGate</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e73a3c785ad1e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ec45f1f49db305</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer: Frontend</t>
+          <t>Data Scientist- Senior Associate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LogicGate</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e08efe5897e8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e1d05c355c99b1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer: Frontend</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LogicGate</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, FAISS, Pinecone, Azure ML, MLflow, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8a47ad97c2d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer: Frontend</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LogicGate</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, FAISS, Pinecone, Azure ML, MLflow, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdffc06c5ccc1b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer: Frontend</t>
+          <t>Data Scientist- Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LogicGate</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d194fe052b34b6</t>
+          <t>https://www.indeed.com/viewjob?jk=34c8e676c573105d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer: Frontend</t>
+          <t>Data Scientist- Associate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LogicGate</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed11f229285ca52</t>
+          <t>https://www.indeed.com/viewjob?jk=01493cd41c21f205</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Security Platform</t>
+          <t>Data Scientist- Associate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Snowflake, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7a17ecc5d35899</t>
+          <t>https://www.indeed.com/viewjob?jk=2e76642072900750</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Snowflake, Databricks, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Data Lake, Terraform, Git, Snowflake, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Scientist 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>University of New Mexico</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Whitehall, MI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476365429fdab851</t>
+          <t>https://www.indeed.com/viewjob?jk=83bd526a8fcb6448</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Burger King, US&amp;C</t>
+          <t>Product Engineer II – On-premises Kubernetes, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Snowflake, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, AKS, Jenkins, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,357 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87bae5a9ff1cc5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1571c5751e3372dd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RTOS Developer for Medical Devices</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Unetixs Vascular, Inc.</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Warwick, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e72a84c6e4f04693</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, XGBoost, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2507413e8e83b165</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Raymond James</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=762bbacf77cb18ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, Kubernetes</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0850cc691e58d361</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer IV 4P/648</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4P Consulting Inc.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Jenkins, Git, MySQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d757f556f0fd1a1</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Databricks, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40e86e53af8b9918</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Consultant, Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dell Technologies</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Round Rock, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3acc4d34dc74f501</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, Snowflake, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca89fd407d4ce0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, Snowflake, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=067ad61add8e8462</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Burlington, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, Snowflake, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca2b32d2d5f67cab</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Enterprise Data Analyst</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cee167b709c3701b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-06.xlsx
+++ b/daily_matches/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Redshift, BigQuery, Data Lake, Snowflake, BigQuery, Redshift, Hadoop</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, EC2, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Graybar</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Clayton, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, EC2, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b455422eee9334</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ontario, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, FastAPI, Docker, Kubernetes</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, EC2, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a8022f39595ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Azure ML, MLflow, Docker, CI/CD, GitHub Actions, Git, Databricks</t>
+          <t>Data Scientist, RAG, FAISS, Pinecone, S3, Glue, CI/CD, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6ee13b18ffe86d</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer- Senior Associate</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Docker, Kubernetes, AKS, CI/CD, Git</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7921646131415cec</t>
+          <t>https://www.indeed.com/viewjob?jk=b502cf0690019205</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer- Senior Associate</t>
+          <t>Senior Software Engineer – Telecom Orchestration &amp; Provisioning</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>OXIO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Docker, Kubernetes, AKS, CI/CD, Git</t>
+          <t>LangChain, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86909537359158b4</t>
+          <t>https://www.indeed.com/viewjob?jk=041d291df691bd82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer- Senior Associate</t>
+          <t>AI ML Operations Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Occidental</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Docker, Kubernetes, AKS, CI/CD, Git</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Databricks, NoSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc876921c22ef16</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff7b7eea2b225b7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Machine Learning Engineer, Sign-Up Flow Optimization</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Kinesis, Docker, CI/CD, Jenkins, Terraform, Databricks, Redshift</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, Git, BigQuery, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
+          <t>https://www.indeed.com/viewjob?jk=bf75e7ace01e5bff</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Applications Engineer</t>
+          <t>Senior AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SEEQ</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Azure ML, Data Lake, CI/CD, Snowflake, Databricks, Tableau, Power BI</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4f1d887d28de9ce1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RNGD</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Metairie, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, AKS, Git, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8999ba90c762227</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef3dd717fe3b47a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist- Senior Associate</t>
+          <t>AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f33a2b9912522b</t>
+          <t>https://www.indeed.com/viewjob?jk=21daf22bbd2e931c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist- Senior Associate</t>
+          <t>Senior AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ec45f1f49db305</t>
+          <t>https://www.indeed.com/viewjob?jk=8e76d75d932909a0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist- Senior Associate</t>
+          <t>Senior AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e1d05c355c99b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f913892d63499061</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, FAISS, Pinecone, Azure ML, MLflow, Databricks, PySpark</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
+          <t>https://www.indeed.com/viewjob?jk=fe2c7c68d61e5bd7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Senior AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, FAISS, Pinecone, Azure ML, MLflow, Databricks, PySpark</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=01ed7d5a25eb1cc5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist- Associate</t>
+          <t>AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c8e676c573105d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1c0bdeee2ee1ec</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist- Associate</t>
+          <t>AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01493cd41c21f205</t>
+          <t>https://www.indeed.com/viewjob?jk=d2386cee1a9ea922</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist- Associate</t>
+          <t>AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, AKS, Git, Databricks, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e76642072900750</t>
+          <t>https://www.indeed.com/viewjob?jk=06e9685308e22788</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Terraform, Git, Snowflake, Databricks, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b52c488dc9036a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist 1</t>
+          <t>Senior AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>University of New Mexico</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bd526a8fcb6448</t>
+          <t>https://www.indeed.com/viewjob?jk=3a11d937ef0c562e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Product Engineer II – On-premises Kubernetes, ArcGIS Enterprise</t>
+          <t>AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, Jenkins, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1571c5751e3372dd</t>
+          <t>https://www.indeed.com/viewjob?jk=909cc1e632a4146a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior AI Engineer (AIMS Martek)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Renaissance Learning</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72a84c6e4f04693</t>
+          <t>https://www.indeed.com/viewjob?jk=ed87bf68d6a5980f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Scientist I</t>
+          <t>Forward-Deployed Solutions Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, XGBoost, PySpark, Python, SQL, R, Scala, Hypothesis Testing</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2507413e8e83b165</t>
+          <t>https://www.indeed.com/viewjob?jk=adb9b5c484a993d7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Pre-Sales Solutions Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Raymond James</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R, Hypothesis Testing</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762bbacf77cb18ad</t>
+          <t>https://www.indeed.com/viewjob?jk=11a709923b831460</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, Kubernetes</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0850cc691e58d361</t>
+          <t>https://www.indeed.com/viewjob?jk=77fbfed937d65f55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer IV 4P/648</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e86e53af8b9918</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd211ee67f981d5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Consultant, Machine Learning Engineer</t>
+          <t>Intermediate Software Engineer - Artificial Intelligence (AI)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Tucows</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+          <t>LLaMA, Mistral, Hugging Face, TensorFlow, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acc4d34dc74f501</t>
+          <t>https://www.indeed.com/viewjob?jk=47ad4c66a593a1d0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineering Intern</t>
+          <t>Senior Engineer- Artificial Intelligence</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Tucows</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S3, CI/CD, Snowflake, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca89fd407d4ce0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c54d187f85f73130</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineering Intern</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, CI/CD, Snowflake, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>Synapse, CI/CD, Snowflake, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067ad61add8e8462</t>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineering Intern</t>
+          <t>CCB Risk Program Associate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Burlington, VT, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, CI/CD, Snowflake, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, Git, Hadoop, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca2b32d2d5f67cab</t>
+          <t>https://www.indeed.com/viewjob?jk=1e712a8c19edbada</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Analyst</t>
+          <t>Data Scientist Associate</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,147 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee167b709c3701b</t>
+          <t>https://www.indeed.com/viewjob?jk=24080c070a358b58</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Applied AIML Data Scientist-Senior Associate</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e05e648b664d1c70</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Cloud Architect - Hybrid</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dartmouth Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Lebanon, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Terraform, Git, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9de2570b75ee18b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Agentic AI Architect- Columbus, OH</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RSHARMA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d324b428a97692</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Backend/Java/Cloud</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Git, Kafka, Cassandra, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=082fb91999b02eb2</t>
         </is>
       </c>
     </row>
